--- a/artfynd/A 11552-2024 artfynd.xlsx
+++ b/artfynd/A 11552-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>115429716</v>
+        <v>115429499</v>
       </c>
       <c r="B2" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,39 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Älggårdsberget, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>590337</v>
+        <v>590468</v>
       </c>
       <c r="R2" t="n">
-        <v>7006699</v>
+        <v>7006692</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -770,27 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>115429506</v>
+        <v>115429500</v>
       </c>
       <c r="B3" t="n">
-        <v>79558</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>590430</v>
+        <v>590439</v>
       </c>
       <c r="R3" t="n">
-        <v>7006722</v>
+        <v>7006644</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -884,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>115429714</v>
+        <v>115429476</v>
       </c>
       <c r="B4" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,39 +880,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Älggårdsberget, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>590349</v>
+        <v>590439</v>
       </c>
       <c r="R4" t="n">
-        <v>7006682</v>
+        <v>7006644</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -979,27 +954,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Dennis Pålsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>115429476</v>
+        <v>115429495</v>
       </c>
       <c r="B5" t="n">
-        <v>90332</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>590439</v>
+        <v>590404</v>
       </c>
       <c r="R5" t="n">
-        <v>7006644</v>
+        <v>7006652</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1093,37 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>115429495</v>
+        <v>115429520</v>
       </c>
       <c r="B6" t="n">
-        <v>90352</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>590404</v>
+        <v>590423</v>
       </c>
       <c r="R6" t="n">
-        <v>7006652</v>
+        <v>7006648</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1195,15 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>115429520</v>
+        <v>115429506</v>
       </c>
       <c r="B7" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1211,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>590423</v>
+        <v>590430</v>
       </c>
       <c r="R7" t="n">
-        <v>7006648</v>
+        <v>7006722</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1297,15 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>115429484</v>
+        <v>115429507</v>
       </c>
       <c r="B8" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1313,39 +1268,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Älggårdsberget, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>590360</v>
+        <v>590348</v>
       </c>
       <c r="R8" t="n">
-        <v>7006650</v>
+        <v>7006663</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1404,15 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>115429499</v>
+        <v>115429484</v>
       </c>
       <c r="B9" t="n">
-        <v>90615</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1420,34 +1365,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Älggårdsberget, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>590468</v>
+        <v>590360</v>
       </c>
       <c r="R9" t="n">
-        <v>7006692</v>
+        <v>7006650</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1509,12 +1459,7 @@
         <v>115429485</v>
       </c>
       <c r="B10" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1613,15 +1558,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>115429487</v>
+        <v>115429486</v>
       </c>
       <c r="B11" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1658,10 +1598,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>590348</v>
+        <v>590354</v>
       </c>
       <c r="R11" t="n">
-        <v>7006658</v>
+        <v>7006656</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1720,15 +1660,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>115429500</v>
+        <v>115429487</v>
       </c>
       <c r="B12" t="n">
-        <v>90615</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1736,34 +1671,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Älggårdsberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>590439</v>
+        <v>590348</v>
       </c>
       <c r="R12" t="n">
-        <v>7006644</v>
+        <v>7006658</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1825,12 +1765,7 @@
         <v>115429488</v>
       </c>
       <c r="B13" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1929,15 +1864,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>115429507</v>
+        <v>115429713</v>
       </c>
       <c r="B14" t="n">
-        <v>79558</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1945,34 +1875,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Älggårdsberget, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>590348</v>
+        <v>590400</v>
       </c>
       <c r="R14" t="n">
-        <v>7006663</v>
+        <v>7006771</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2019,27 +1954,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>115429715</v>
+        <v>115429714</v>
       </c>
       <c r="B15" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2076,10 +2006,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>590340</v>
+        <v>590349</v>
       </c>
       <c r="R15" t="n">
-        <v>7006693</v>
+        <v>7006682</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2138,15 +2068,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>115429486</v>
+        <v>115429715</v>
       </c>
       <c r="B16" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2183,10 +2108,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>590354</v>
+        <v>590340</v>
       </c>
       <c r="R16" t="n">
-        <v>7006656</v>
+        <v>7006693</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2233,27 +2158,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Dennis Pålsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>115429713</v>
+        <v>115429716</v>
       </c>
       <c r="B17" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2290,10 +2210,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>590400</v>
+        <v>590337</v>
       </c>
       <c r="R17" t="n">
-        <v>7006771</v>
+        <v>7006699</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2349,6 +2269,108 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>115429717</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Älggårdsberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>590320</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7006700</v>
+      </c>
+      <c r="S18" t="n">
+        <v>20</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Helgum</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-03-26</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-03-26</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Dennis Pålsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 11552-2024 artfynd.xlsx
+++ b/artfynd/A 11552-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AZ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115429499</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115429500</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115429476</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115429495</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115429520</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115429506</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115429507</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1453,6 +1493,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115429484</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1555,6 +1600,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115429485</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1657,6 +1707,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115429486</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1759,6 +1814,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115429487</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1861,6 +1921,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115429488</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1963,6 +2028,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115429713</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2065,6 +2135,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115429714</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2167,6 +2242,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115429715</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2269,6 +2349,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115429716</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2371,8 +2456,32 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115429717</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>